--- a/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-structure/inputsheet-structure.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/inputsheet-structure/inputsheet-structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\inputsheet-structure\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\inputsheet-structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{864165A0-026C-4FD0-8FE7-727CDC65A7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCD0EF4-9AD2-45A1-8205-2DB440814751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3550" yWindow="2480" windowWidth="20600" windowHeight="11960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3276" yWindow="1608" windowWidth="24588" windowHeight="13248" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="inputsheet-structure" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="59">
   <si>
     <t>■</t>
     <phoneticPr fontId="1"/>
@@ -810,6 +810,96 @@
     </rPh>
     <rPh sb="17" eb="19">
       <t>フクゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST001_TableInfoHeader</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST002_ColumnHeader</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST003_AttributeAndTargetMemo</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST004_ResultAndMessageColumns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST005a_NumAndDateTime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>数値型、日付型項目のデータ設定例</t>
+    <rPh sb="0" eb="3">
+      <t>スウチガタ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ヒヅケガタ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>セッテイレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST005b_TextAndChar</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST005c_OtherDataType</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バイナリ型、BLOB型データの設定例</t>
+    <rPh sb="4" eb="5">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>セッテイレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文字型項目のデータ設定例</t>
+    <rPh sb="0" eb="2">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガタ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>セッテイレイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>IST006_WorksheetProtection</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>項目ヘッダ部のワークシート保護</t>
+    <rPh sb="0" eb="2">
+      <t>コウモク</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホゴ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -911,6 +1001,658 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>233081</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>170909</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="47" name="グループ化 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{207E2E86-62F6-15B6-5760-3F660291D690}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466166" y="11465859"/>
+          <a:ext cx="13187080" cy="1990744"/>
+          <a:chOff x="472441" y="6396318"/>
+          <a:chExt cx="13362789" cy="1950403"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="45" name="図 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D32DBAE-463E-80B5-0724-D96CD1A16566}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="472441" y="6400800"/>
+            <a:ext cx="6641053" cy="1945921"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="46" name="図 45">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9482116-F386-5BD1-DED8-9AC43DD8C20D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7230034" y="6396318"/>
+            <a:ext cx="6605196" cy="1943920"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>82701</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>132063</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="51" name="グループ化 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30FE3596-2C30-918A-7F97-9716F2005CD7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="466165" y="699247"/>
+          <a:ext cx="13502865" cy="4793710"/>
+          <a:chOff x="472440" y="685800"/>
+          <a:chExt cx="13570101" cy="4704063"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="48" name="図 47">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56A2FD9F-99EA-49BF-8314-9A358AE570D4}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="472440" y="685800"/>
+            <a:ext cx="13570101" cy="4704063"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="50" name="正方形/長方形 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E5D2ED7-16A7-4B02-8093-CE58B104CE7F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="735554" y="2102224"/>
+            <a:ext cx="13086678" cy="409014"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>8964</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>24429</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>221710</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="53" name="グループ化 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0274379-1F08-A4AD-993E-C3BF7061E524}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="475129" y="6060141"/>
+          <a:ext cx="13435629" cy="4883357"/>
+          <a:chOff x="481404" y="5943600"/>
+          <a:chExt cx="13502865" cy="4793710"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="49" name="図 48">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2043FA9-2C6C-486B-94C4-53AD3E189417}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="481404" y="5943600"/>
+            <a:ext cx="13502865" cy="4793710"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="52" name="正方形/長方形 51">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBB2B4D3-0E9A-4F58-B24A-1F3A02914589}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="735554" y="7741024"/>
+            <a:ext cx="1449593" cy="1026459"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>215154</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>215153</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>193963</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="58" name="グループ化 57">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96EC5F24-623A-9390-2800-3E410DE43B29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="448236" y="14200094"/>
+          <a:ext cx="12000480" cy="4724400"/>
+          <a:chOff x="472440" y="13716000"/>
+          <a:chExt cx="12045752" cy="4634753"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="56" name="図 55">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7E56B7B-7E38-4BC3-A648-42F5E265B198}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="472440" y="13716000"/>
+            <a:ext cx="12045752" cy="4634753"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="57" name="正方形/長方形 56">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{88C3720A-C307-45BF-9BD5-B37D4E9E4896}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7145318" y="15540317"/>
+            <a:ext cx="4577827" cy="2371165"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+            <a:prstTxWarp prst="textNoShape">
+              <a:avLst/>
+            </a:prstTxWarp>
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>194312</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>212027</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="61" name="図 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{90240757-2C3C-4E9A-CDB7-6611ACC12F34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="472441" y="19659600"/>
+          <a:ext cx="13681711" cy="4098227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>194311</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>96046</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="62" name="図 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC6B7EC7-8826-0484-7992-26905CB5B9BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="472440" y="24460200"/>
+          <a:ext cx="13681711" cy="4896647"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>194312</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>55222</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="63" name="図 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B502E7-CBCD-8D29-09D8-E03DF5D84FEF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="472441" y="30861001"/>
+          <a:ext cx="13681711" cy="5084421"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="bg1">
+              <a:lumMod val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>215154</xdr:colOff>
+      <xdr:row>162</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>224118</xdr:colOff>
+      <xdr:row>183</xdr:row>
+      <xdr:rowOff>25064</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="64" name="図 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE706ABA-3619-D6F5-6515-BA82286A3A3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="448236" y="37759342"/>
+          <a:ext cx="12496800" cy="4919793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>48683</xdr:rowOff>
@@ -934,8 +1676,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="691776" y="743448"/>
-          <a:ext cx="6056033" cy="5032687"/>
+          <a:off x="694765" y="747930"/>
+          <a:ext cx="6096373" cy="5064063"/>
           <a:chOff x="698500" y="436033"/>
           <a:chExt cx="6146800" cy="4969934"/>
         </a:xfrm>
@@ -3136,8 +3878,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="254000" y="7933766"/>
-          <a:ext cx="8520057" cy="6579719"/>
+          <a:off x="255494" y="7984566"/>
+          <a:ext cx="8573845" cy="6621554"/>
           <a:chOff x="234950" y="6400801"/>
           <a:chExt cx="8641080" cy="6496049"/>
         </a:xfrm>
@@ -3400,8 +4142,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="15583649"/>
-          <a:ext cx="8520057" cy="5343485"/>
+          <a:off x="233082" y="15683755"/>
+          <a:ext cx="8573845" cy="5377850"/>
           <a:chOff x="234950" y="14240437"/>
           <a:chExt cx="8641080" cy="5274756"/>
         </a:xfrm>
@@ -3840,8 +4582,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="67464747"/>
-          <a:ext cx="10650071" cy="8259649"/>
+          <a:off x="233082" y="67899536"/>
+          <a:ext cx="10717306" cy="8311942"/>
           <a:chOff x="217714" y="64949614"/>
           <a:chExt cx="10800443" cy="8155060"/>
         </a:xfrm>
@@ -4005,8 +4747,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="231588" y="58396522"/>
-          <a:ext cx="10650071" cy="7946338"/>
+          <a:off x="233082" y="58773040"/>
+          <a:ext cx="10717306" cy="7997138"/>
           <a:chOff x="234950" y="56500487"/>
           <a:chExt cx="10801350" cy="7844738"/>
         </a:xfrm>
@@ -4283,8 +5025,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="240658" y="77219466"/>
-          <a:ext cx="10645802" cy="6857194"/>
+          <a:off x="242152" y="77717008"/>
+          <a:ext cx="10714532" cy="6902017"/>
           <a:chOff x="226785" y="75309984"/>
           <a:chExt cx="10800443" cy="6767548"/>
         </a:xfrm>
@@ -4614,8 +5356,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9039410" y="1579284"/>
-          <a:ext cx="6060968" cy="3673815"/>
+          <a:off x="9097681" y="1588249"/>
+          <a:ext cx="6099815" cy="3697721"/>
           <a:chOff x="9170519" y="1561355"/>
           <a:chExt cx="6148374" cy="3626328"/>
         </a:xfrm>
@@ -6045,8 +6787,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="18534529" y="1875117"/>
-          <a:ext cx="4176059" cy="5353423"/>
+          <a:off x="18654058" y="1887070"/>
+          <a:ext cx="4202954" cy="5387788"/>
           <a:chOff x="18810940" y="1513541"/>
           <a:chExt cx="4236571" cy="5284693"/>
         </a:xfrm>
@@ -7349,8 +8091,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249731" y="89474701"/>
-          <a:ext cx="10645802" cy="6853188"/>
+          <a:off x="251225" y="90051430"/>
+          <a:ext cx="10714532" cy="6896517"/>
           <a:chOff x="253093" y="88321242"/>
           <a:chExt cx="10800443" cy="6766529"/>
         </a:xfrm>
@@ -7468,8 +8210,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="249731" y="97571218"/>
-          <a:ext cx="10645802" cy="6853190"/>
+          <a:off x="251225" y="98200242"/>
+          <a:ext cx="10714532" cy="6896519"/>
           <a:chOff x="253093" y="96313171"/>
           <a:chExt cx="10800443" cy="6766531"/>
         </a:xfrm>
@@ -7827,128 +8569,215 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{247D8D20-CE8B-4D82-A6C6-EA8B8BD03E4C}">
-  <dimension ref="B3:CD573"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:C572"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="4" width="3.09765625" style="1"/>
+    <col min="5" max="5" width="15.09765625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="33.796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="69.19921875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:82" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="CD3" s="2"/>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B33" s="2"/>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="2"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="2"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" s="2"/>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="2"/>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B106" s="2"/>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B130" s="2"/>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B145" s="2"/>
-    </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B164" s="2"/>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B168" s="2"/>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B183" s="2"/>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B203" s="2"/>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B222" s="2"/>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B236" s="2"/>
-    </row>
-    <row r="249" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B249" s="2"/>
-    </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B258" s="2"/>
-    </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B277" s="2"/>
-    </row>
-    <row r="289" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B289" s="2"/>
-    </row>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B301" s="2"/>
-    </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B330" s="2"/>
-    </row>
-    <row r="333" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B333" s="3"/>
-    </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B356" s="2"/>
-    </row>
-    <row r="365" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B365" s="2"/>
-    </row>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B30" s="2"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B55" s="2"/>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B62" s="2"/>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B79" s="2"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A85" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C86" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B89" s="2"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B103" s="2"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A107" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C108" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B129" s="2"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A133" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="C134" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="B144" s="2"/>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A160" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="161" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="C161" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="163" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B163" s="2"/>
+    </row>
+    <row r="167" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B167" s="2"/>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B182" s="2"/>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B202" s="2"/>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B221" s="2"/>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B235" s="2"/>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B248" s="2"/>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B257" s="2"/>
+    </row>
+    <row r="276" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B276" s="2"/>
+    </row>
+    <row r="288" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B288" s="2"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B300" s="2"/>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B329" s="2"/>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B332" s="3"/>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B355" s="2"/>
+    </row>
+    <row r="364" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B364" s="2"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B382" s="2"/>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B384" s="2"/>
-    </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B410" s="2"/>
-    </row>
-    <row r="419" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B419" s="2"/>
-    </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B436" s="2"/>
-    </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B469" s="2"/>
-    </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B511" s="2"/>
-    </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B538" s="2"/>
-    </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="B573" s="2"/>
+    <row r="409" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B409" s="2"/>
+    </row>
+    <row r="418" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B418" s="2"/>
+    </row>
+    <row r="435" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B435" s="2"/>
+    </row>
+    <row r="468" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B468" s="2"/>
+    </row>
+    <row r="510" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B510" s="2"/>
+    </row>
+    <row r="537" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B537" s="2"/>
+    </row>
+    <row r="572" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B572" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29FA320-DA47-41A9-9EA7-7E68689E0E1F}">
   <dimension ref="A1:ED573"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -8346,7 +9175,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -8366,7 +9195,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN4" s="1" t="s">
         <v>40</v>
       </c>
@@ -8374,7 +9203,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN5" s="1" t="s">
         <v>37</v>
       </c>
@@ -8382,7 +9211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN6" s="1" t="s">
         <v>41</v>
       </c>
@@ -8390,12 +9219,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.45">
       <c r="CD7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -8403,15 +9232,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -8419,20 +9248,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B66" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B67" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>0</v>
       </c>
@@ -8440,15 +9269,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B106" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>0</v>
       </c>
@@ -8456,18 +9285,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B145" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B164" s="2"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
@@ -8475,12 +9304,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B169" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
         <v>0</v>
       </c>
@@ -8488,20 +9317,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B185" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B203" s="2"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -8509,20 +9338,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B223" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B224" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B236" s="2"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
         <v>0</v>
       </c>
@@ -8530,28 +9359,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B250" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B251" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B252" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B258" s="2"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
         <v>0</v>
       </c>
@@ -8559,20 +9388,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B290" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B291" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B301" s="2"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A330" s="1" t="s">
         <v>0</v>
       </c>
@@ -8580,25 +9409,25 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B331" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B332" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B333" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B356" s="2"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A365" s="1" t="s">
         <v>0</v>
       </c>
@@ -8606,15 +9435,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B366" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A384" s="1" t="s">
         <v>0</v>
       </c>
@@ -8622,20 +9451,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B385" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B386" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B410" s="2"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
         <v>0</v>
       </c>
@@ -8643,29 +9472,29 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B420" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B421" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B436" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B469" s="2"/>
     </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B511" s="2"/>
     </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B538" s="2"/>
     </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B573" s="2"/>
     </row>
   </sheetData>
